--- a/static/files/catalog_uplotneniy.xlsx
+++ b/static/files/catalog_uplotneniy.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Материалы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Профили" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Условия" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Каталог" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Материалы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Профили" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Условия" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Каталог" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="README" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Каталог'!$A$1:$P$601</definedName>
@@ -38640,7 +38640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -38728,13 +38728,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Примечание: коды и аналоги в этом шаблоне — демонстрационные. Замените на ваши правила/стандарты.</t>
-        </is>
-      </c>
-    </row>
+    <row r="15" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
